--- a/three_statement_model.xlsx
+++ b/three_statement_model.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Debt Schedule" sheetId="6" r:id="rId6"/>
     <sheet name="Projection Model" sheetId="7" r:id="rId7"/>
     <sheet name="Ratio Dashboard" sheetId="8" r:id="rId8"/>
+    <sheet name="DCF Valuation" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -94,6 +95,11 @@
   <cols>
     <col min="1" max="1" width="42" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -229,6 +235,193 @@
       </c>
       <c r="B16" s="4">
         <f>'Projection Model'!F28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DCF Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>'DCF Valuation'!B21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>DCF Equity Value</t>
+        </is>
+      </c>
+      <c r="B18" s="4">
+        <f>'DCF Valuation'!B22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Implied Price / Share (INR)</t>
+        </is>
+      </c>
+      <c r="B19" s="4">
+        <f>'DCF Valuation'!B23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="7">
+        <is>
+          <t>2D Sensitivity: FY2030 Net Debt / EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr" s="2">
+        <is>
+          <t>Growth \ Margin</t>
+        </is>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.02</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-0.01</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="G22" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5">
+        <v>-0.02</v>
+      </c>
+      <c r="C23">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B23))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+C$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B23))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+D$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B23))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+E$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F23">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B23))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+F$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B23))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+G$22))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5">
+        <v>-0.01</v>
+      </c>
+      <c r="C24">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B24))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+C$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B24))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+D$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B24))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+E$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B24))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+F$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B24))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+G$22))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="5">
+        <v>0.0</v>
+      </c>
+      <c r="C25">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B25))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+C$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B25))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+D$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B25))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+E$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B25))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+F$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B25))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+G$22))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="C26">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B26))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+C$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B26))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+D$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B26))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+E$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B26))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+F$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B26))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+G$22))),0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="C27">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B27))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+C$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B27))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+D$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B27))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+E$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B27))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+F$22))),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <f>IFERROR((('Projection Model'!$F$25-'Projection Model'!$F$19)/(('Projection Model'!$F$5*(1+$B27))*(('Projection Model'!$F$9/'Projection Model'!$F$5)+G$22))),0)</f>
         <v>0</v>
       </c>
     </row>
@@ -3211,4 +3404,388 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="13" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>DCF Valuation</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr" s="2">
+        <is>
+          <t>Line Item</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr" s="2">
+        <is>
+          <t>FY2026E</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr" s="2">
+        <is>
+          <t>FY2027E</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr" s="2">
+        <is>
+          <t>FY2028E</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>FY2029E</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr" s="2">
+        <is>
+          <t>FY2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B4" s="4">
+        <f>'Projection Model'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <f>'Projection Model'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <f>'Projection Model'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <f>'Projection Model'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
+        <f>'Projection Model'!F5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NOPAT (EBIT*(1-tax))</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>'Projection Model'!B11*(1-INDEX(Assumptions!$B$26:$F$26,1,1))</f>
+        <v>0</v>
+      </c>
+      <c r="C5" s="4">
+        <f>'Projection Model'!C11*(1-INDEX(Assumptions!$B$26:$F$26,1,2))</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="4">
+        <f>'Projection Model'!D11*(1-INDEX(Assumptions!$B$26:$F$26,1,3))</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <f>'Projection Model'!E11*(1-INDEX(Assumptions!$B$26:$F$26,1,4))</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <f>'Projection Model'!F11*(1-INDEX(Assumptions!$B$26:$F$26,1,5))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="B6" s="4">
+        <f>'Projection Model'!B10</f>
+        <v>0</v>
+      </c>
+      <c r="C6" s="4">
+        <f>'Projection Model'!C10</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="4">
+        <f>'Projection Model'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <f>'Projection Model'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <f>'Projection Model'!F10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>-'Projection Model'!B35</f>
+        <v>0</v>
+      </c>
+      <c r="C7" s="4">
+        <f>-'Projection Model'!C35</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="4">
+        <f>-'Projection Model'!D35</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="4">
+        <f>-'Projection Model'!E35</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="4">
+        <f>-'Projection Model'!F35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Change in NWC</t>
+        </is>
+      </c>
+      <c r="B8" s="4">
+        <f>'Projection Model'!B33</f>
+        <v>0</v>
+      </c>
+      <c r="C8" s="4">
+        <f>'Projection Model'!C33</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="4">
+        <f>'Projection Model'!D33</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="4">
+        <f>'Projection Model'!E33</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="4">
+        <f>'Projection Model'!F33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free Cash Flow</t>
+        </is>
+      </c>
+      <c r="B9" s="4">
+        <f>B5+B6-B7-B8</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="4">
+        <f>C5+C6-C7-C8</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="4">
+        <f>D5+D6-D7-D8</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="4">
+        <f>E5+E6-E7-E8</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="4">
+        <f>F5+F6-F7-F8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr" s="7">
+        <is>
+          <t>WACC</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr" s="7">
+        <is>
+          <t>Terminal Growth</t>
+        </is>
+      </c>
+      <c r="B12" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr" s="7">
+        <is>
+          <t>Shares Outstanding (bn)</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>6.76</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr" s="7">
+        <is>
+          <t>Net Debt (FY2030E)</t>
+        </is>
+      </c>
+      <c r="B14" s="4">
+        <f>'Projection Model'!F25-'Projection Model'!F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr" s="3">
+        <is>
+          <t>Discount Factor</t>
+        </is>
+      </c>
+      <c r="B16">
+        <f>1/(1+$B$11)^1</f>
+        <v>0</v>
+      </c>
+      <c r="C16">
+        <f>1/(1+$B$11)^2</f>
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <f>1/(1+$B$11)^3</f>
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <f>1/(1+$B$11)^4</f>
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <f>1/(1+$B$11)^5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr" s="3">
+        <is>
+          <t>PV of FCF</t>
+        </is>
+      </c>
+      <c r="B17" s="4">
+        <f>B9*B16</f>
+        <v>0</v>
+      </c>
+      <c r="C17" s="4">
+        <f>C9*C16</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="4">
+        <f>D9*D16</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="4">
+        <f>E9*E16</f>
+        <v>0</v>
+      </c>
+      <c r="F17" s="4">
+        <f>F9*F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr" s="7">
+        <is>
+          <t>Terminal Value (at FY2030E)</t>
+        </is>
+      </c>
+      <c r="F18" s="4">
+        <f>F9*(1+$B$12)/($B$11-$B$12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr" s="7">
+        <is>
+          <t>PV of Terminal Value</t>
+        </is>
+      </c>
+      <c r="F19" s="4">
+        <f>F18*F16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr" s="3">
+        <is>
+          <t>Enterprise Value</t>
+        </is>
+      </c>
+      <c r="B21" s="4">
+        <f>SUM(B17:F17)+F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr" s="3">
+        <is>
+          <t>Equity Value</t>
+        </is>
+      </c>
+      <c r="B22" s="4">
+        <f>B21-B14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr" s="3">
+        <is>
+          <t>Implied Price per Share (INR)</t>
+        </is>
+      </c>
+      <c r="B23" s="4">
+        <f>B22/B13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr" s="7">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr" s="7">
+        <is>
+          <t>WACC &gt; Terminal Growth?</t>
+        </is>
+      </c>
+      <c r="B26">
+        <f>IF(B11&gt;B12,"OK","Fix Inputs")</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>